--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:02</t>
+    <t xml:space="preserve">2026-09-09 19:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:29</t>
+    <t xml:space="preserve">2026-09-17 03:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 03:58</t>
+    <t xml:space="preserve">2026-09-27 02:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:22</t>
+    <t xml:space="preserve">2026-10-03 00:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_aysen.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">apoyo</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 00:16</t>
+    <t xml:space="preserve">2026-10-05 05:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Aysen</t>
+    <t xml:space="preserve">Region de Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">Capitán Prat</t>
@@ -843,7 +840,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>34.27</v>
@@ -857,7 +854,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>35.39</v>
@@ -871,7 +868,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>29.66</v>
